--- a/Jerel_Smith_2026_Roadmap_1.xlsx
+++ b/Jerel_Smith_2026_Roadmap_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns8="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:ns9="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <ns1:AlternateContent>
-    <ns1:Choice Requires="x15">
-      <ns2:absPath url="https://bhphoto-my.sharepoint.com/personal/jerelscs_bhphoto_com/Documents/"/>
-    </ns1:Choice>
-  </ns1:AlternateContent>
-  <ns3:revisionPtr revIDLastSave="3306" documentId="8_{4EA0C5C9-16B6-DF4F-ABD4-AAB2FD3EB27E}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{ADDA14AF-E055-3F41-A32D-745653C0C105}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bhphoto-my.sharepoint.com/personal/jerelscs_bhphoto_com/Documents/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3306" documentId="8_{4EA0C5C9-16B6-DF4F-ABD4-AAB2FD3EB27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADDA14AF-E055-3F41-A32D-745653C0C105}"/>
   <bookViews>
-    <workbookView xWindow="21600" yWindow="7560" windowWidth="38400" windowHeight="21000" activeTab="2" ns6:uid="{A076985F-6CFB-DB49-A7AE-C6E23E578DA1}"/>
+    <workbookView xWindow="21600" yWindow="7560" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{A076985F-6CFB-DB49-A7AE-C6E23E578DA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Quaterly" sheetId="2" r:id="rId1"/>
@@ -23,8 +23,8 @@
     <sheet name="Metrics (Don't Touch)" sheetId="9" r:id="rId8"/>
     <sheet name="GA4 (Don't Touch)" sheetId="10" r:id="rId9"/>
     <sheet name="Roadmap 26-27 (Don't Touch)" sheetId="12" r:id="rId10"/>
-    <sheet name="Roadmap (Auto)" sheetId="13" r:id="rId15" state="visible"/>
-    <sheet name="Roadmap Calc (Don’t Touch)" sheetId="14" r:id="rId16" state="hidden"/>
+    <sheet name="Roadmap (Auto)" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Roadmap Calc (Don’t Touch)" sheetId="14" state="hidden" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Initiative Tracker'!$A$4:$I$4</definedName>
@@ -33,19 +33,19 @@
   </definedNames>
   <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0" fullCalcOnLoad="1"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <ns8:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <ns9:calcFeatures>
-        <ns9:feature name="microsoft.com:RD"/>
-        <ns9:feature name="microsoft.com:Single"/>
-        <ns9:feature name="microsoft.com:FV"/>
-        <ns9:feature name="microsoft.com:CNMTM"/>
-        <ns9:feature name="microsoft.com:LET_WF"/>
-        <ns9:feature name="microsoft.com:LAMBDA_WF"/>
-        <ns9:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </ns9:calcFeatures>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -2610,13 +2610,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mmm yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="mmm yy"/>
   </numFmts>
-  <fonts count="38" ns2:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4561,11 +4561,11 @@
     </mruColors>
   </colors>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
